--- a/lojas-proprias/pwr_reports/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-08-17 - 2026-08-23).xlsx
+++ b/lojas-proprias/pwr_reports/KEYS Service Main Service Exceptions - Lojas Corporativas (Stores)(2026-08-17 - 2026-08-23).xlsx
@@ -227,88 +227,91 @@
     <t>22</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>R$ 52.432,55</t>
-  </si>
-  <si>
-    <t>521.5</t>
-  </si>
-  <si>
-    <t>320.4</t>
-  </si>
-  <si>
-    <t>5.51</t>
-  </si>
-  <si>
-    <t>16.0</t>
-  </si>
-  <si>
-    <t>3.6</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>R$ 55.271,12</t>
+  </si>
+  <si>
+    <t>582.3</t>
+  </si>
+  <si>
+    <t>378.8</t>
+  </si>
+  <si>
+    <t>5.65</t>
+  </si>
+  <si>
+    <t>16.2</t>
+  </si>
+  <si>
+    <t>3.7</t>
   </si>
   <si>
     <t>6.5</t>
   </si>
   <si>
-    <t>57.3%</t>
-  </si>
-  <si>
-    <t>14.5%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>53.4%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>1.8%</t>
+    <t>1.7%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>5.6%</t>
-  </si>
-  <si>
-    <t>3.5%</t>
-  </si>
-  <si>
-    <t>2.9%</t>
-  </si>
-  <si>
-    <t>1128.0</t>
-  </si>
-  <si>
-    <t>974.0</t>
+    <t>5.2%</t>
+  </si>
+  <si>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>2.7%</t>
+  </si>
+  <si>
+    <t>1239.0</t>
+  </si>
+  <si>
+    <t>1081.0</t>
   </si>
   <si>
     <t>42.0</t>
   </si>
   <si>
-    <t>7.0</t>
-  </si>
-  <si>
-    <t>122.0</t>
-  </si>
-  <si>
-    <t>27.0</t>
-  </si>
-  <si>
     <t>8.0</t>
   </si>
   <si>
-    <t>380.0</t>
-  </si>
-  <si>
-    <t>237.0</t>
-  </si>
-  <si>
-    <t>192.0</t>
-  </si>
-  <si>
-    <t>120.0</t>
+    <t>135.0</t>
+  </si>
+  <si>
+    <t>29.0</t>
+  </si>
+  <si>
+    <t>9.0</t>
+  </si>
+  <si>
+    <t>410.0</t>
+  </si>
+  <si>
+    <t>269.0</t>
+  </si>
+  <si>
+    <t>218.0</t>
+  </si>
+  <si>
+    <t>1.6%</t>
+  </si>
+  <si>
+    <t>127.0</t>
   </si>
   <si>
     <t>1</t>
@@ -933,7 +936,7 @@
         <v>19504</v>
       </c>
       <c r="B2" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c t="s" r="C2" s="4">
         <v>51</v>
@@ -964,40 +967,40 @@
       </c>
       <c r="L2" s="4"/>
       <c r="M2" s="5">
-        <v>37301.547500000001</v>
+        <v>61115.299999999996</v>
       </c>
       <c r="N2" s="6">
-        <v>215</v>
+        <v>570</v>
       </c>
       <c r="O2" s="6">
-        <v>128</v>
+        <v>385</v>
       </c>
       <c r="P2" s="7">
-        <v>3.981633980582524</v>
+        <v>3.9917560931899638</v>
       </c>
       <c r="Q2" s="8">
-        <v>13.86171875</v>
+        <v>14.233722857142856</v>
       </c>
       <c r="R2" s="8">
-        <v>2.7429679687499999</v>
+        <v>3.0813418181818184</v>
       </c>
       <c r="S2" s="8">
         <v>7</v>
       </c>
       <c r="T2" s="9">
-        <v>0.71875</v>
+        <v>0.66753246753246753</v>
       </c>
       <c r="U2" s="9">
-        <v>0.0625</v>
+        <v>0.057142857142857141</v>
       </c>
       <c r="V2" s="9">
-        <v>0.015625</v>
+        <v>0.0051948051948051948</v>
       </c>
       <c r="W2" s="9">
         <v>0</v>
       </c>
       <c r="X2" s="9">
-        <v>0.015625</v>
+        <v>0.012987012987012988</v>
       </c>
       <c r="Y2" s="9">
         <v>0</v>
@@ -1006,19 +1009,19 @@
         <v>0</v>
       </c>
       <c r="AA2" s="9">
-        <v>0.03125</v>
+        <v>0.020779220779220779</v>
       </c>
       <c r="AB2" s="9">
-        <v>0</v>
+        <v>0.012987012987012988</v>
       </c>
       <c r="AC2" s="9">
-        <v>0</v>
+        <v>0.0051948051948051948</v>
       </c>
       <c r="AD2" s="6">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="AE2" s="6">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="AF2" s="6">
         <v>2</v>
@@ -1027,28 +1030,28 @@
         <v>0</v>
       </c>
       <c r="AH2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AI2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AJ2" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK2" s="6">
+        <v>8</v>
+      </c>
+      <c r="AL2" s="6">
+        <v>5</v>
+      </c>
+      <c r="AM2" s="6">
         <v>2</v>
       </c>
-      <c r="AI2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AJ2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AK2" s="6">
-        <v>4</v>
-      </c>
-      <c r="AL2" s="6">
-        <v>0</v>
-      </c>
-      <c r="AM2" s="6">
-        <v>0</v>
-      </c>
       <c r="AN2" s="9">
-        <v>0</v>
+        <v>0.0025974025974025974</v>
       </c>
       <c r="AO2" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="s" r="AP2" s="4">
         <v>58</v>
@@ -1243,7 +1246,7 @@
         <v>19507</v>
       </c>
       <c r="B4" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C4" s="4">
         <v>51</v>
@@ -1274,61 +1277,61 @@
       </c>
       <c r="L4" s="4"/>
       <c r="M4" s="5">
-        <v>50843.216666666653</v>
+        <v>74836.419999999998</v>
       </c>
       <c r="N4" s="6">
-        <v>229</v>
+        <v>761</v>
       </c>
       <c r="O4" s="6">
-        <v>173</v>
+        <v>585</v>
       </c>
       <c r="P4" s="7">
-        <v>5.9999255605381165</v>
+        <v>7.7833333774834434</v>
       </c>
       <c r="Q4" s="8">
-        <v>15.025241040462427</v>
+        <v>17.400455897435897</v>
       </c>
       <c r="R4" s="8">
-        <v>2.1694278106508875</v>
+        <v>2.5748986086956522</v>
       </c>
       <c r="S4" s="8">
         <v>7</v>
       </c>
       <c r="T4" s="9">
-        <v>0.56647398843930641</v>
+        <v>0.43931623931623931</v>
       </c>
       <c r="U4" s="9">
-        <v>0.086705202312138727</v>
+        <v>0.083760683760683755</v>
       </c>
       <c r="V4" s="9">
-        <v>0.0057803468208092483</v>
+        <v>0.0017094017094017094</v>
       </c>
       <c r="W4" s="9">
-        <v>0.0057803468199999998</v>
+        <v>0.0017094017089999999</v>
       </c>
       <c r="X4" s="9">
-        <v>0.023121387283236993</v>
+        <v>0.017094017094017096</v>
       </c>
       <c r="Y4" s="9">
-        <v>0.011560693641618497</v>
+        <v>0.0068376068376068376</v>
       </c>
       <c r="Z4" s="9">
         <v>0</v>
       </c>
       <c r="AA4" s="9">
-        <v>0.04046242774566474</v>
+        <v>0.039316239316239315</v>
       </c>
       <c r="AB4" s="9">
-        <v>0.017341040462427744</v>
+        <v>0.020512820512820513</v>
       </c>
       <c r="AC4" s="9">
-        <v>0.011560693641618497</v>
+        <v>0.010256410256410256</v>
       </c>
       <c r="AD4" s="6">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="AE4" s="6">
-        <v>15</v>
+        <v>49</v>
       </c>
       <c r="AF4" s="6">
         <v>1</v>
@@ -1337,22 +1340,22 @@
         <v>1</v>
       </c>
       <c r="AH4" s="6">
+        <v>10</v>
+      </c>
+      <c r="AI4" s="6">
         <v>4</v>
       </c>
-      <c r="AI4" s="6">
-        <v>2</v>
-      </c>
       <c r="AJ4" s="6">
         <v>0</v>
       </c>
       <c r="AK4" s="6">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="AL4" s="6">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AM4" s="6">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AN4" s="9">
         <v>0</v>
@@ -1592,7 +1595,7 @@
         <v>568</v>
       </c>
       <c r="O6" s="6">
-        <v>336</v>
+        <v>408</v>
       </c>
       <c r="P6" s="7">
         <v>5.5802949458483759</v>
@@ -1610,37 +1613,37 @@
         <v>0.54656862745098034</v>
       </c>
       <c r="U6" s="9">
-        <v>0.16369047619047619</v>
+        <v>0.15196078431372548</v>
       </c>
       <c r="V6" s="9">
-        <v>0.0059523809523809521</v>
+        <v>0.0049019607843137254</v>
       </c>
       <c r="W6" s="9">
         <v>0</v>
       </c>
       <c r="X6" s="9">
-        <v>0.0089285714285714281</v>
+        <v>0.0073529411764705881</v>
       </c>
       <c r="Y6" s="9">
         <v>0</v>
       </c>
       <c r="Z6" s="9">
-        <v>0.002976190476190476</v>
+        <v>0.0024509803921568627</v>
       </c>
       <c r="AA6" s="9">
         <v>0</v>
       </c>
       <c r="AB6" s="9">
-        <v>0.10119047619047619</v>
+        <v>0.088235294117647065</v>
       </c>
       <c r="AC6" s="9">
-        <v>0.041666666666666664</v>
+        <v>0.044117647058823532</v>
       </c>
       <c r="AD6" s="6">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="AE6" s="6">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="AF6" s="6">
         <v>2</v>
@@ -1661,16 +1664,16 @@
         <v>0</v>
       </c>
       <c r="AL6" s="6">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AM6" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AN6" s="9">
-        <v>0.0089285714285714281</v>
+        <v>0.0098039215686274508</v>
       </c>
       <c r="AO6" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c t="s" r="AP6" s="4">
         <v>58</v>
@@ -2330,7 +2333,7 @@
         <v>19519</v>
       </c>
       <c r="B11" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C11" s="4">
         <v>51</v>
@@ -2361,61 +2364,61 @@
       </c>
       <c r="L11" s="4"/>
       <c r="M11" s="5">
-        <v>119257.76333333332</v>
+        <v>122580.37</v>
       </c>
       <c r="N11" s="6">
-        <v>1169</v>
+        <v>1391</v>
       </c>
       <c r="O11" s="6">
-        <v>551</v>
+        <v>671</v>
       </c>
       <c r="P11" s="7">
-        <v>6.3175139351446106</v>
+        <v>6.6416605592347313</v>
       </c>
       <c r="Q11" s="8">
-        <v>17.067090199637025</v>
+        <v>17.45481877794337</v>
       </c>
       <c r="R11" s="8">
-        <v>3.5538533944954129</v>
+        <v>3.555103167420814</v>
       </c>
       <c r="S11" s="8">
         <v>7</v>
       </c>
       <c r="T11" s="9">
-        <v>0.39382940108892922</v>
+        <v>0.36065573770491804</v>
       </c>
       <c r="U11" s="9">
-        <v>0.19600725952813067</v>
+        <v>0.19672131147540983</v>
       </c>
       <c r="V11" s="9">
-        <v>0.0054446460980036296</v>
+        <v>0.0044709388971684054</v>
       </c>
       <c r="W11" s="9">
-        <v>0.001814882032</v>
+        <v>0.001490312965</v>
       </c>
       <c r="X11" s="9">
-        <v>0.014519056261343012</v>
+        <v>0.011922503725782414</v>
       </c>
       <c r="Y11" s="9">
-        <v>0.0018148820326678765</v>
+        <v>0.0014903129657228018</v>
       </c>
       <c r="Z11" s="9">
-        <v>0.0018148820326678765</v>
+        <v>0.0029806259314456036</v>
       </c>
       <c r="AA11" s="9">
-        <v>0.025408348457350273</v>
+        <v>0.026825633383010434</v>
       </c>
       <c r="AB11" s="9">
-        <v>0.043557168784029036</v>
+        <v>0.046199701937406856</v>
       </c>
       <c r="AC11" s="9">
-        <v>0.1161524500907441</v>
+        <v>0.11326378539493294</v>
       </c>
       <c r="AD11" s="6">
-        <v>115</v>
+        <v>139</v>
       </c>
       <c r="AE11" s="6">
-        <v>108</v>
+        <v>132</v>
       </c>
       <c r="AF11" s="6">
         <v>3</v>
@@ -2430,16 +2433,16 @@
         <v>1</v>
       </c>
       <c r="AJ11" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AK11" s="6">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="AL11" s="6">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="AM11" s="6">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2522,7 +2525,7 @@
         <v>388</v>
       </c>
       <c r="O12" s="6">
-        <v>208</v>
+        <v>280</v>
       </c>
       <c r="P12" s="7">
         <v>5.1372368421052634</v>
@@ -2540,16 +2543,16 @@
         <v>0.61071428571428577</v>
       </c>
       <c r="U12" s="9">
-        <v>0.081730769230769232</v>
+        <v>0.089285714285714288</v>
       </c>
       <c r="V12" s="9">
-        <v>0.014423076923076924</v>
+        <v>0.010714285714285714</v>
       </c>
       <c r="W12" s="9">
         <v>0</v>
       </c>
       <c r="X12" s="9">
-        <v>0.02403846153846154</v>
+        <v>0.021428571428571429</v>
       </c>
       <c r="Y12" s="9">
         <v>0</v>
@@ -2561,16 +2564,16 @@
         <v>0</v>
       </c>
       <c r="AB12" s="9">
-        <v>0.004807692307692308</v>
+        <v>0.0071428571428571426</v>
       </c>
       <c r="AC12" s="9">
-        <v>0</v>
+        <v>0.014285714285714285</v>
       </c>
       <c r="AD12" s="6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AE12" s="6">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="AF12" s="6">
         <v>3</v>
@@ -2579,7 +2582,7 @@
         <v>0</v>
       </c>
       <c r="AH12" s="6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI12" s="6">
         <v>0</v>
@@ -2591,16 +2594,16 @@
         <v>0</v>
       </c>
       <c r="AL12" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AM12" s="6">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AN12" s="9">
-        <v>0.038461538461538464</v>
+        <v>0.035714285714285712</v>
       </c>
       <c r="AO12" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c t="s" r="AP12" s="4">
         <v>58</v>
@@ -2640,7 +2643,7 @@
         <v>19560</v>
       </c>
       <c r="B13" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C13" s="4">
         <v>51</v>
@@ -2671,61 +2674,61 @@
       </c>
       <c r="L13" s="4"/>
       <c r="M13" s="5">
-        <v>74539.371666666659</v>
+        <v>77302.589999999997</v>
       </c>
       <c r="N13" s="6">
-        <v>643</v>
+        <v>811</v>
       </c>
       <c r="O13" s="6">
-        <v>465</v>
+        <v>591</v>
       </c>
       <c r="P13" s="7">
-        <v>10.524129588607595</v>
+        <v>11.248996110414053</v>
       </c>
       <c r="Q13" s="8">
-        <v>17.765985376344084</v>
+        <v>18.564241116751269</v>
       </c>
       <c r="R13" s="8">
-        <v>1.5267637566137566</v>
+        <v>1.5624670634920634</v>
       </c>
       <c r="S13" s="8">
         <v>6</v>
       </c>
       <c r="T13" s="9">
-        <v>0.55913978494623651</v>
+        <v>0.51438240270727575</v>
       </c>
       <c r="U13" s="9">
-        <v>0.55483870967741933</v>
+        <v>0.45346869712351945</v>
       </c>
       <c r="V13" s="9">
-        <v>0.0021505376344086021</v>
+        <v>0.0016920473773265651</v>
       </c>
       <c r="W13" s="9">
         <v>0</v>
       </c>
       <c r="X13" s="9">
-        <v>0.0043010752688172043</v>
+        <v>0.005076142131979695</v>
       </c>
       <c r="Y13" s="9">
-        <v>0.010752688172043012</v>
+        <v>0.0084602368866328256</v>
       </c>
       <c r="Z13" s="9">
         <v>0</v>
       </c>
       <c r="AA13" s="9">
-        <v>0.43010752688172044</v>
+        <v>0.34179357021996615</v>
       </c>
       <c r="AB13" s="9">
-        <v>0.16559139784946236</v>
+        <v>0.14213197969543148</v>
       </c>
       <c r="AC13" s="9">
-        <v>0.098924731182795697</v>
+        <v>0.077834179357021999</v>
       </c>
       <c r="AD13" s="6">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="AE13" s="6">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="AF13" s="6">
         <v>1</v>
@@ -2734,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="AH13" s="6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI13" s="6">
         <v>5</v>
@@ -2743,10 +2746,10 @@
         <v>0</v>
       </c>
       <c r="AK13" s="6">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AL13" s="6">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AM13" s="6">
         <v>46</v>
@@ -2834,7 +2837,7 @@
         <v>337</v>
       </c>
       <c r="O14" s="6">
-        <v>176</v>
+        <v>239</v>
       </c>
       <c r="P14" s="7">
         <v>5.6490432024169186</v>
@@ -2852,7 +2855,7 @@
         <v>0.53361344537815125</v>
       </c>
       <c r="U14" s="9">
-        <v>0.096590909090909088</v>
+        <v>0.083682008368200833</v>
       </c>
       <c r="V14" s="9">
         <v>0</v>
@@ -2861,7 +2864,7 @@
         <v>0</v>
       </c>
       <c r="X14" s="9">
-        <v>0.022727272727272728</v>
+        <v>0.020920502092050208</v>
       </c>
       <c r="Y14" s="9">
         <v>0</v>
@@ -2870,19 +2873,19 @@
         <v>0</v>
       </c>
       <c r="AA14" s="9">
-        <v>0.056818181818181816</v>
+        <v>0.050209205020920501</v>
       </c>
       <c r="AB14" s="9">
-        <v>0.005681818181818182</v>
+        <v>0.0041841004184100415</v>
       </c>
       <c r="AC14" s="9">
-        <v>0.011363636363636364</v>
+        <v>0.008368200836820083</v>
       </c>
       <c r="AD14" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AE14" s="6">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AF14" s="6">
         <v>0</v>
@@ -2891,7 +2894,7 @@
         <v>0</v>
       </c>
       <c r="AH14" s="6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AI14" s="6">
         <v>0</v>
@@ -2900,7 +2903,7 @@
         <v>0</v>
       </c>
       <c r="AK14" s="6">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AL14" s="6">
         <v>1</v>
@@ -3088,7 +3091,7 @@
         <v>389</v>
       </c>
       <c r="O16" s="6">
-        <v>158</v>
+        <v>207</v>
       </c>
       <c r="P16" s="7">
         <v>5.2341330666666668</v>
@@ -3106,37 +3109,37 @@
         <v>0.51690821256038644</v>
       </c>
       <c r="U16" s="9">
-        <v>0.15189873417721519</v>
+        <v>0.13526570048309178</v>
       </c>
       <c r="V16" s="9">
-        <v>0.025316455696202531</v>
+        <v>0.01932367149758454</v>
       </c>
       <c r="W16" s="9">
         <v>0</v>
       </c>
       <c r="X16" s="9">
-        <v>0.018987341772151899</v>
+        <v>0.01932367149758454</v>
       </c>
       <c r="Y16" s="9">
-        <v>0.012658227848101266</v>
+        <v>0.0096618357487922701</v>
       </c>
       <c r="Z16" s="9">
-        <v>0.0063291139240506328</v>
+        <v>0.004830917874396135</v>
       </c>
       <c r="AA16" s="9">
-        <v>0.012658227848101266</v>
+        <v>0.01932367149758454</v>
       </c>
       <c r="AB16" s="9">
-        <v>0.037974683544303799</v>
+        <v>0.033816425120772944</v>
       </c>
       <c r="AC16" s="9">
         <v>0</v>
       </c>
       <c r="AD16" s="6">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="AE16" s="6">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="AF16" s="6">
         <v>4</v>
@@ -3145,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="AH16" s="6">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI16" s="6">
         <v>2</v>
@@ -3154,19 +3157,19 @@
         <v>1</v>
       </c>
       <c r="AK16" s="6">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AL16" s="6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM16" s="6">
         <v>0</v>
       </c>
       <c r="AN16" s="9">
-        <v>0.075949367088607597</v>
+        <v>0.06280193236714976</v>
       </c>
       <c r="AO16" s="6">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c t="s" r="AP16" s="4">
         <v>58</v>
@@ -3243,7 +3246,7 @@
         <v>343</v>
       </c>
       <c r="O17" s="6">
-        <v>166</v>
+        <v>222</v>
       </c>
       <c r="P17" s="7">
         <v>2.6359781437125749</v>
@@ -3261,7 +3264,7 @@
         <v>0.83783783783783783</v>
       </c>
       <c r="U17" s="9">
-        <v>0.054216867469879519</v>
+        <v>0.04954954954954955</v>
       </c>
       <c r="V17" s="9">
         <v>0</v>
@@ -3270,28 +3273,28 @@
         <v>0</v>
       </c>
       <c r="X17" s="9">
-        <v>0.006024096385542169</v>
+        <v>0.0045045045045045045</v>
       </c>
       <c r="Y17" s="9">
-        <v>0.006024096385542169</v>
+        <v>0.0045045045045045045</v>
       </c>
       <c r="Z17" s="9">
         <v>0</v>
       </c>
       <c r="AA17" s="9">
-        <v>0.012048192771084338</v>
+        <v>0.0090090090090090089</v>
       </c>
       <c r="AB17" s="9">
-        <v>0.006024096385542169</v>
+        <v>0.0045045045045045045</v>
       </c>
       <c r="AC17" s="9">
         <v>0</v>
       </c>
       <c r="AD17" s="6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE17" s="6">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF17" s="6">
         <v>0</v>
@@ -3318,10 +3321,10 @@
         <v>0</v>
       </c>
       <c r="AN17" s="9">
-        <v>0.042168674698795178</v>
+        <v>0.040540540540540543</v>
       </c>
       <c r="AO17" s="6">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c t="s" r="AP17" s="4">
         <v>58</v>
@@ -4036,13 +4039,13 @@
         <v>0.67027027027027031</v>
       </c>
       <c r="U22" s="9">
-        <v>0.13243243243243244</v>
+        <v>0.13513513513513514</v>
       </c>
       <c r="V22" s="9">
         <v>0.010810810810810811</v>
       </c>
       <c r="W22" s="9">
-        <v>0.0027027027020000002</v>
+        <v>0.005405405405</v>
       </c>
       <c r="X22" s="9">
         <v>0.0027027027027027029</v>
@@ -4066,13 +4069,13 @@
         <v>50</v>
       </c>
       <c r="AE22" s="6">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AF22" s="6">
         <v>4</v>
       </c>
       <c r="AG22" s="6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AH22" s="6">
         <v>1</v>
@@ -4385,10 +4388,10 @@
         <v>98</v>
       </c>
       <c t="s" r="AN24" s="11">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c t="s" r="AO24" s="11">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AP24" s="12"/>
       <c t="s" r="AQ24" s="12">
@@ -4405,10 +4408,10 @@
         <v>59</v>
       </c>
       <c t="s" r="AX24" s="11">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="AY24" s="11">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AZ24" s="12"/>
       <c r="BA24" s="12"/>
